--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>40001</v>
+        <v>30008</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>40001</v>
+        <v>30008</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>重命名当前阵容</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>40002</v>
+        <v>30009</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>40002</v>
+        <v>30009</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>出战阵容</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2303,14 +2303,14 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>40003</v>
+        <v>30010</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>40003</v>
+        <v>30010</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>音频</t>
+          <t>清空当前阵容</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2321,14 +2321,14 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>40998</v>
+        <v>30011</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>40998</v>
+        <v>30011</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>已开启</t>
+          <t>是否清空当前阵容的所有魔物？</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>40999</v>
+        <v>40001</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>40999</v>
+        <v>40001</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>已关闭</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>游戏设置</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>41001</v>
+        <v>40002</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>41001</v>
+        <v>40002</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2375,14 +2375,14 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>42001</v>
+        <v>40003</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>42001</v>
+        <v>40003</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>屏幕分辨率</t>
+          <t>音频</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2393,14 +2393,14 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>42002</v>
+        <v>40998</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>42002</v>
+        <v>40998</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>锁定帧数</t>
+          <t>已开启</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -2411,14 +2411,14 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>42003</v>
+        <v>40999</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>42003</v>
+        <v>40999</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>帧数</t>
+          <t>已关闭</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -2429,14 +2429,14 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>43001</v>
+        <v>41001</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>43001</v>
+        <v>41001</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>音乐音量</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -2447,14 +2447,14 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>43002</v>
+        <v>42001</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>43002</v>
+        <v>42001</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>屏幕分辨率</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -2465,32 +2465,32 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>49001</v>
+        <v>42002</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>49001</v>
+        <v>42002</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>锁定帧数</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>游戏系统</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>49002</v>
+        <v>42003</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>49002</v>
+        <v>42003</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>返回主界面</t>
+          <t>帧数</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -2501,14 +2501,14 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>49003</v>
+        <v>43001</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>49003</v>
+        <v>43001</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>退出游戏</t>
+          <t>音乐音量</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -2519,14 +2519,14 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>49004</v>
+        <v>43002</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>49004</v>
+        <v>43002</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>退出战斗</t>
+          <t>音效音量</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -2537,32 +2537,32 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>50001</v>
+        <v>49001</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>50001</v>
+        <v>49001</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>游戏设置</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>游戏系统</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>50002</v>
+        <v>49002</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>50002</v>
+        <v>49002</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>击杀</t>
+          <t>返回主界面</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -2573,14 +2573,14 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>50003</v>
+        <v>49003</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>50003</v>
+        <v>49003</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>经验</t>
+          <t>退出游戏</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -2591,14 +2591,14 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>50004</v>
+        <v>49004</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>50004</v>
+        <v>49004</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>承伤</t>
+          <t>退出战斗</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -2609,32 +2609,32 @@
     </row>
     <row r="87" ht="12" customHeight="1" s="1">
       <c r="A87" s="0" t="n">
-        <v>50005</v>
+        <v>50001</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>50005</v>
+        <v>50001</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>当前征程：{0}/{1}</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>战斗主界面</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>50006</v>
+        <v>50002</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>50006</v>
+        <v>50002</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>魔力不足</t>
+          <t>击杀</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -2645,158 +2645,158 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>50007</v>
+        <v>50003</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>50007</v>
+        <v>50003</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>经验</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>50008</v>
+        <v>50004</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>50008</v>
+        <v>50004</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>受疗</t>
+          <t>承伤</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>50101</v>
+        <v>50005</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>50101</v>
+        <v>50005</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>当前征程：{0}/{1}</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗主界面</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>51001</v>
+        <v>50006</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>51001</v>
+        <v>50006</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠</t>
+          <t>魔力不足</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>战斗深渊馈赠</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>51002</v>
+        <v>50007</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>51002</v>
+        <v>50007</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>51003</v>
+        <v>50008</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>51003</v>
+        <v>50008</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>受疗</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>52001</v>
+        <v>50101</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>52001</v>
+        <v>50101</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>奖励选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>52002</v>
+        <v>51001</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>52002</v>
+        <v>51001</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗深渊馈赠</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>52003</v>
+        <v>51002</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>52003</v>
+        <v>51002</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -2807,14 +2807,14 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>52004</v>
+        <v>51003</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>52004</v>
+        <v>51003</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -2825,50 +2825,50 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>52005</v>
+        <v>52001</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>52005</v>
+        <v>52001</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>奖励选择</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53000</v>
+        <v>52002</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>53000</v>
+        <v>52002</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53001</v>
+        <v>52003</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>53001</v>
+        <v>52003</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -2879,14 +2879,14 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53002</v>
+        <v>52004</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>53002</v>
+        <v>52004</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -2897,14 +2897,14 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53003</v>
+        <v>52005</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>53003</v>
+        <v>52005</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -2915,32 +2915,32 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53004</v>
+        <v>53000</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>53004</v>
+        <v>53000</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>终焉议会</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53005</v>
+        <v>53001</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>53005</v>
+        <v>53001</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -2951,14 +2951,14 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53006</v>
+        <v>53002</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>53006</v>
+        <v>53002</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -2969,14 +2969,14 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>53007</v>
+        <v>53003</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>53007</v>
+        <v>53003</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -2987,14 +2987,14 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>53008</v>
+        <v>53004</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>53008</v>
+        <v>53004</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -3005,14 +3005,14 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>53009</v>
+        <v>53005</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>53009</v>
+        <v>53005</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3023,14 +3023,14 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>53010</v>
+        <v>53006</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>53010</v>
+        <v>53006</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3041,14 +3041,14 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>53011</v>
+        <v>53007</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>53011</v>
+        <v>53007</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3059,14 +3059,14 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>53012</v>
+        <v>53008</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>53012</v>
+        <v>53008</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3077,14 +3077,14 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>53013</v>
+        <v>53009</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>53013</v>
+        <v>53009</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3095,14 +3095,14 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>53014</v>
+        <v>53010</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>53014</v>
+        <v>53010</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>当前议案通过率:{0}%</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>53015</v>
+        <v>53011</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>53015</v>
+        <v>53011</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>议案:</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3149,32 +3149,32 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55001</v>
+        <v>53013</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>55001</v>
+        <v>53013</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55002</v>
+        <v>53014</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>55002</v>
+        <v>53014</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>55003</v>
+        <v>53015</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>55003</v>
+        <v>53015</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>议案:</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>标题</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>55004</v>
+        <v>54001</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>55004</v>
+        <v>54001</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,32 +3221,32 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>55005</v>
+        <v>55001</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>55005</v>
+        <v>55001</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>55006</v>
+        <v>55002</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>55006</v>
+        <v>55002</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,14 +3257,14 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>55007</v>
+        <v>55003</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>55007</v>
+        <v>55003</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3275,32 +3275,32 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>60000</v>
+        <v>55004</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>60000</v>
+        <v>55004</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>60001</v>
+        <v>55005</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>60001</v>
+        <v>55005</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3311,14 +3311,14 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>60002</v>
+        <v>55006</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>60002</v>
+        <v>55006</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3329,14 +3329,14 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>61001</v>
+        <v>55007</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>61001</v>
+        <v>55007</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>61002</v>
+        <v>60000</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>61002</v>
+        <v>60000</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>61003</v>
+        <v>60001</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>61003</v>
+        <v>60001</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3383,14 +3383,14 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>61004</v>
+        <v>60002</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>61004</v>
+        <v>60002</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3401,14 +3401,14 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>61005</v>
+        <v>61001</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>61005</v>
+        <v>61001</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3419,14 +3419,14 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>61006</v>
+        <v>61002</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>61006</v>
+        <v>61002</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3437,14 +3437,14 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>61007</v>
+        <v>61003</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>61007</v>
+        <v>61003</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>献祭成功，等级提升！</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3455,14 +3455,14 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>61008</v>
+        <v>61004</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>61008</v>
+        <v>61004</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>献祭失败，祭品已消耗</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -3473,14 +3473,14 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>61009</v>
+        <v>61005</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>61009</v>
+        <v>61005</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>经验值未达到100%</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3491,32 +3491,32 @@
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>61010</v>
+        <v>61006</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>61010</v>
+        <v>61006</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>请选择要榨汁的目标魔物</t>
+          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>魔汁机</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>61011</v>
+        <v>61007</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>61011</v>
+        <v>61007</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>开始榨汁</t>
+          <t>献祭成功，等级提升！</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3527,14 +3527,14 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>61012</v>
+        <v>61008</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>61012</v>
+        <v>61008</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>最多只能投入{0}只魔物</t>
+          <t>献祭失败，祭品已消耗</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3545,14 +3545,14 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>61013</v>
+        <v>61009</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>61013</v>
+        <v>61009</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>选择榨汁魔物</t>
+          <t>经验值未达到100%</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3563,32 +3563,32 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>62001</v>
+        <v>61010</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>62001</v>
+        <v>61010</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>请选择要榨汁的目标魔物</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
         <is>
-          <t>生物研究</t>
+          <t>魔汁机</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>62002</v>
+        <v>61011</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>62002</v>
+        <v>61011</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>开始榨汁</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3599,14 +3599,14 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>62003</v>
+        <v>61012</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>62003</v>
+        <v>61012</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>最多只能投入{0}只魔物</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3617,14 +3617,14 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>62004</v>
+        <v>61013</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>62004</v>
+        <v>61013</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>选择榨汁魔物</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -3635,50 +3635,50 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>62005</v>
+        <v>62001</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>62005</v>
+        <v>62001</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>63001</v>
+        <v>62002</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>63001</v>
+        <v>62002</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>63002</v>
+        <v>62003</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>63002</v>
+        <v>62003</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -3689,14 +3689,14 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>63003</v>
+        <v>62004</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>63003</v>
+        <v>62004</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -3707,46 +3707,46 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>64001</v>
+        <v>62005</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>64001</v>
+        <v>62005</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>64002</v>
+        <v>63001</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>64002</v>
+        <v>63001</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>65001</v>
+        <v>63002</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>65001</v>
+        <v>63002</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -3755,56 +3755,56 @@
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>生物属性添加</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>80001</v>
+        <v>64001</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>80001</v>
+        <v>64001</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>80002</v>
+        <v>64002</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>80002</v>
+        <v>64002</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -3815,68 +3815,68 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>80003</v>
+        <v>65001</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>80003</v>
+        <v>65001</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物属性添加</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>80004</v>
+        <v>70001</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>80004</v>
+        <v>70001</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>80005</v>
+        <v>80001</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>80005</v>
+        <v>80001</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="157" ht="12" customHeight="1" s="1">
       <c r="A157" s="0" t="n">
-        <v>80006</v>
+        <v>80002</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>80006</v>
+        <v>80002</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -3887,14 +3887,14 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>80007</v>
+        <v>80003</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>80007</v>
+        <v>80003</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -3905,14 +3905,14 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>80008</v>
+        <v>80004</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>80008</v>
+        <v>80004</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -3923,14 +3923,14 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>80009</v>
+        <v>80005</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>80009</v>
+        <v>80005</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -3941,14 +3941,14 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>80010</v>
+        <v>80006</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>80010</v>
+        <v>80006</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -3959,14 +3959,14 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>80013</v>
+        <v>80007</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>80013</v>
+        <v>80007</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>进阶成功，稀有度提升！</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -3977,32 +3977,32 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>90001</v>
+        <v>80008</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>90001</v>
+        <v>80008</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>90002</v>
+        <v>80009</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>90002</v>
+        <v>80009</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4013,32 +4013,32 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1000001</v>
+        <v>80010</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>1000001</v>
+        <v>80010</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1000002</v>
+        <v>80013</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>1000002</v>
+        <v>80013</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>进阶成功，稀有度提升！</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4049,122 +4049,122 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1001001</v>
+        <v>90001</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>1001001</v>
+        <v>90001</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1002001</v>
+        <v>90002</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>1002001</v>
+        <v>90002</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1002002</v>
+        <v>1000001</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>1002002</v>
+        <v>1000001</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
-        <v>1002003</v>
-      </c>
-      <c r="B170" t="n">
-        <v>1002003</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>装备</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>弹窗-道具选择</t>
+      <c r="A170" s="0" t="n">
+        <v>1000002</v>
+      </c>
+      <c r="B170" s="0" t="n">
+        <v>1000002</v>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
-        <v>1002004</v>
-      </c>
-      <c r="B171" t="n">
-        <v>1002004</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>是否要丢弃该道具？</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>弹窗-道具选择</t>
+      <c r="A171" s="0" t="n">
+        <v>1001001</v>
+      </c>
+      <c r="B171" s="0" t="n">
+        <v>1001001</v>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>等级.{0}</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,68 +4175,68 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1004001</v>
+        <v>1002003</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>1004001</v>
+        <v>1002003</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1004002</v>
+        <v>1002004</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>1004002</v>
+        <v>1002004</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>是否要丢弃该道具？</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1005001</v>
+        <v>1003001</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>1005001</v>
+        <v>1003001</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>1005002</v>
+        <v>1003002</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>1005002</v>
+        <v>1003002</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4247,68 +4247,68 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>1005003</v>
+        <v>1004001</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>1005003</v>
+        <v>1004001</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000001</v>
+        <v>1004002</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>2000001</v>
+        <v>1004002</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000002</v>
+        <v>1005001</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>2000002</v>
+        <v>1005001</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000003</v>
+        <v>1005002</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>2000003</v>
+        <v>1005002</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4319,14 +4319,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000004</v>
+        <v>1005003</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>2000004</v>
+        <v>1005003</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,32 +4337,32 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000005</v>
+        <v>2000001</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>2000005</v>
+        <v>2000001</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000006</v>
+        <v>2000002</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>2000006</v>
+        <v>2000002</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4373,14 +4373,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000007</v>
+        <v>2000003</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>2000007</v>
+        <v>2000003</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4391,14 +4391,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000008</v>
+        <v>2000004</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>2000008</v>
+        <v>2000004</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>2000009</v>
+        <v>2000005</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>2000009</v>
+        <v>2000005</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4427,14 +4427,14 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>2000010</v>
+        <v>2000006</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>2000010</v>
+        <v>2000006</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4445,14 +4445,14 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>2000011</v>
+        <v>2000007</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>2000011</v>
+        <v>2000007</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4463,14 +4463,14 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="n">
-        <v>2000014</v>
+        <v>2000008</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>2000014</v>
+        <v>2000008</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4481,14 +4481,14 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="n">
-        <v>2000015</v>
+        <v>2000009</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>2000015</v>
+        <v>2000009</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4499,14 +4499,14 @@
     </row>
     <row r="192" ht="12" customHeight="1" s="1">
       <c r="A192" s="0" t="n">
-        <v>2000016</v>
+        <v>2000010</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>2000016</v>
+        <v>2000010</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4517,14 +4517,14 @@
     </row>
     <row r="193" ht="12" customHeight="1" s="1">
       <c r="A193" s="0" t="n">
-        <v>2000017</v>
+        <v>2000011</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>2000017</v>
+        <v>2000011</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4535,14 +4535,14 @@
     </row>
     <row r="194" ht="12" customHeight="1" s="1">
       <c r="A194" s="0" t="n">
-        <v>2000018</v>
+        <v>2000014</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>2000018</v>
+        <v>2000014</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4553,14 +4553,14 @@
     </row>
     <row r="195" ht="12" customHeight="1" s="1">
       <c r="A195" s="0" t="n">
-        <v>2000019</v>
+        <v>2000015</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>2000019</v>
+        <v>2000015</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4571,14 +4571,14 @@
     </row>
     <row r="196" ht="12" customHeight="1" s="1">
       <c r="A196" s="0" t="n">
-        <v>2000020</v>
+        <v>2000016</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>2000020</v>
+        <v>2000016</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -4589,14 +4589,14 @@
     </row>
     <row r="197" ht="12" customHeight="1" s="1">
       <c r="A197" s="0" t="n">
-        <v>2000021</v>
+        <v>2000017</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>2000021</v>
+        <v>2000017</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -4607,14 +4607,14 @@
     </row>
     <row r="198" ht="12" customHeight="1" s="1">
       <c r="A198" s="0" t="n">
-        <v>2000022</v>
+        <v>2000018</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>2000022</v>
+        <v>2000018</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -4625,14 +4625,14 @@
     </row>
     <row r="199" ht="12" customHeight="1" s="1">
       <c r="A199" s="0" t="n">
-        <v>2000023</v>
+        <v>2000019</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>2000023</v>
+        <v>2000019</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>低等级...</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
@@ -4643,14 +4643,14 @@
     </row>
     <row r="200" ht="12" customHeight="1" s="1">
       <c r="A200" s="0" t="n">
-        <v>2000024</v>
+        <v>2000020</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>2000024</v>
+        <v>2000020</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>高等级...</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -4661,32 +4661,32 @@
     </row>
     <row r="201" ht="12" customHeight="1" s="1">
       <c r="A201" s="0" t="n">
-        <v>3000001</v>
+        <v>2000021</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>3000001</v>
+        <v>2000021</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="202" ht="12" customHeight="1" s="1">
       <c r="A202" s="0" t="n">
-        <v>3000002</v>
+        <v>2000022</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>3000002</v>
+        <v>2000022</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
@@ -4697,14 +4697,14 @@
     </row>
     <row r="203" ht="12" customHeight="1" s="1">
       <c r="A203" s="0" t="n">
-        <v>3000003</v>
+        <v>2000023</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>3000003</v>
+        <v>2000023</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="D203" s="0" t="inlineStr">
@@ -4715,14 +4715,14 @@
     </row>
     <row r="204" ht="12" customHeight="1" s="1">
       <c r="A204" s="0" t="n">
-        <v>3000004</v>
+        <v>2000024</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>3000004</v>
+        <v>2000024</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="D204" s="0" t="inlineStr">
@@ -4732,159 +4732,159 @@
       </c>
     </row>
     <row r="205" ht="12" customHeight="1" s="1">
-      <c r="A205" s="0" t="n">
-        <v>3000005</v>
-      </c>
-      <c r="B205" s="0" t="n">
-        <v>3000005</v>
-      </c>
-      <c r="C205" s="0" t="inlineStr">
-        <is>
-          <t>转生成功！</t>
-        </is>
-      </c>
-      <c r="D205" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A205" t="n">
+        <v>2000026</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2000026</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="206" ht="12" customHeight="1" s="1">
-      <c r="A206" s="0" t="n">
-        <v>4000006</v>
-      </c>
-      <c r="B206" s="0" t="n">
-        <v>4000006</v>
-      </c>
-      <c r="C206" s="0" t="inlineStr">
-        <is>
-          <t>{0}/{1}</t>
-        </is>
-      </c>
-      <c r="D206" s="0" t="inlineStr">
-        <is>
-          <t>Achievement-进度</t>
+      <c r="A206" t="n">
+        <v>2000027</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2000027</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>移动镜头</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="207" ht="12" customHeight="1" s="1">
-      <c r="A207" s="0" t="n">
-        <v>4000008</v>
-      </c>
-      <c r="B207" s="0" t="n">
-        <v>4000008</v>
-      </c>
-      <c r="C207" s="0" t="inlineStr">
-        <is>
-          <t>领取成功！</t>
-        </is>
-      </c>
-      <c r="D207" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A207" t="n">
+        <v>2000028</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2000028</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>互动</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="208" ht="12" customHeight="1" s="1">
-      <c r="A208" s="0" t="n">
-        <v>4000010</v>
-      </c>
-      <c r="B208" s="0" t="n">
-        <v>4000010</v>
-      </c>
-      <c r="C208" s="0" t="inlineStr">
-        <is>
-          <t>游玩时间</t>
-        </is>
-      </c>
-      <c r="D208" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A208" t="n">
+        <v>2000029</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2000029</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>突进</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="209" ht="12" customHeight="1" s="1">
-      <c r="A209" s="0" t="n">
-        <v>4000011</v>
-      </c>
-      <c r="B209" s="0" t="n">
-        <v>4000011</v>
-      </c>
-      <c r="C209" s="0" t="inlineStr">
-        <is>
-          <t>总击杀数</t>
-        </is>
-      </c>
-      <c r="D209" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A209" t="n">
+        <v>2000030</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2000030</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>0倍速</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="210" ht="12" customHeight="1" s="1">
-      <c r="A210" s="0" t="n">
-        <v>4000012</v>
-      </c>
-      <c r="B210" s="0" t="n">
-        <v>4000012</v>
-      </c>
-      <c r="C210" s="0" t="inlineStr">
-        <is>
-          <t>征服通关</t>
-        </is>
-      </c>
-      <c r="D210" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A210" t="n">
+        <v>2000031</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2000031</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2倍速</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="211" ht="12" customHeight="1" s="1">
-      <c r="A211" s="0" t="n">
-        <v>4000013</v>
-      </c>
-      <c r="B211" s="0" t="n">
-        <v>4000013</v>
-      </c>
-      <c r="C211" s="0" t="inlineStr">
-        <is>
-          <t>难度{0}</t>
-        </is>
-      </c>
-      <c r="D211" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A211" t="n">
+        <v>2000032</v>
+      </c>
+      <c r="B211" t="n">
+        <v>2000032</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>加快进攻节奏</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>按键提示气泡</t>
         </is>
       </c>
     </row>
     <row r="212" ht="12" customHeight="1" s="1">
       <c r="A212" s="0" t="n">
-        <v>4000014</v>
+        <v>3000001</v>
       </c>
       <c r="B212" s="0" t="n">
-        <v>4000014</v>
+        <v>3000001</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D212" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="213" ht="12" customHeight="1" s="1">
       <c r="A213" s="0" t="n">
-        <v>4000015</v>
+        <v>3000002</v>
       </c>
       <c r="B213" s="0" t="n">
-        <v>4000015</v>
+        <v>3000002</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D213" s="0" t="inlineStr">
@@ -4895,85 +4895,310 @@
     </row>
     <row r="214" ht="12" customHeight="1" s="1">
       <c r="A214" s="0" t="n">
-        <v>4000016</v>
+        <v>3000003</v>
       </c>
       <c r="B214" s="0" t="n">
-        <v>4000016</v>
+        <v>3000003</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D214" s="0" t="inlineStr">
         <is>
-          <t>Achievement-等级</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="215" ht="12" customHeight="1" s="1">
       <c r="A215" s="0" t="n">
-        <v>4000017</v>
+        <v>3000004</v>
       </c>
       <c r="B215" s="0" t="n">
-        <v>4000017</v>
+        <v>3000004</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D215" s="0" t="inlineStr">
         <is>
-          <t>Achievement-已完成</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="216" ht="12" customHeight="1" s="1">
       <c r="A216" s="0" t="n">
-        <v>4000018</v>
+        <v>3000005</v>
       </c>
       <c r="B216" s="0" t="n">
-        <v>4000018</v>
+        <v>3000005</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t>刷新x{0}</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D216" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠-刷新</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="217" ht="12" customHeight="1" s="1">
       <c r="A217" s="0" t="n">
+        <v>4000006</v>
+      </c>
+      <c r="B217" s="0" t="n">
+        <v>4000006</v>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-进度</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="12" customHeight="1" s="1">
+      <c r="A218" s="0" t="n">
+        <v>4000008</v>
+      </c>
+      <c r="B218" s="0" t="n">
+        <v>4000008</v>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>领取成功！</t>
+        </is>
+      </c>
+      <c r="D218" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="12" customHeight="1" s="1">
+      <c r="A219" s="0" t="n">
+        <v>4000010</v>
+      </c>
+      <c r="B219" s="0" t="n">
+        <v>4000010</v>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>游玩时间</t>
+        </is>
+      </c>
+      <c r="D219" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="12" customHeight="1" s="1">
+      <c r="A220" s="0" t="n">
+        <v>4000011</v>
+      </c>
+      <c r="B220" s="0" t="n">
+        <v>4000011</v>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>总击杀数</t>
+        </is>
+      </c>
+      <c r="D220" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="12" customHeight="1" s="1">
+      <c r="A221" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="B221" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>征服通关</t>
+        </is>
+      </c>
+      <c r="D221" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="12" customHeight="1" s="1">
+      <c r="A222" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B222" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="D222" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="12" customHeight="1" s="1">
+      <c r="A223" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B223" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D223" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="12" customHeight="1" s="1">
+      <c r="A224" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B224" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="D224" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="12" customHeight="1" s="1">
+      <c r="A225" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B225" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D225" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="12" customHeight="1" s="1">
+      <c r="A226" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="B226" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D226" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="n">
+        <v>4000018</v>
+      </c>
+      <c r="B227" s="0" t="n">
+        <v>4000018</v>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>刷新x{0}</t>
+        </is>
+      </c>
+      <c r="D227" s="0" t="inlineStr">
+        <is>
+          <t>深渊馈赠-刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="n">
         <v>4000020</v>
       </c>
-      <c r="B217" s="0" t="n">
+      <c r="B228" s="0" t="n">
         <v>4000020</v>
       </c>
-      <c r="C217" s="0" t="inlineStr">
+      <c r="C228" s="0" t="inlineStr">
         <is>
           <t>随机生成一条该稀有度增益</t>
         </is>
       </c>
-      <c r="D217" s="0" t="inlineStr">
+      <c r="D228" s="0" t="inlineStr">
         <is>
           <t>魔物进阶-随机增益兜底</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="12" customHeight="1" s="1"/>
-    <row r="219" ht="12" customHeight="1" s="1"/>
-    <row r="220" ht="12" customHeight="1" s="1"/>
-    <row r="221" ht="12" customHeight="1" s="1"/>
-    <row r="222" ht="12" customHeight="1" s="1"/>
-    <row r="223" ht="12" customHeight="1" s="1"/>
-    <row r="224" ht="12" customHeight="1" s="1"/>
-    <row r="225" ht="12" customHeight="1" s="1"/>
-    <row r="226" ht="12" customHeight="1" s="1"/>
+    <row r="229">
+      <c r="A229" s="0" t="n">
+        <v>504</v>
+      </c>
+      <c r="B229" s="0" t="n">
+        <v>504</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>是否重新挑战？当前战斗进度将不会保留，战斗将从头开始。</t>
+        </is>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="n">
+        <v>49005</v>
+      </c>
+      <c r="B230" s="0" t="n">
+        <v>49005</v>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>重新挑战</t>
+        </is>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
     <row r="278" ht="12" customHeight="1" s="1"/>
     <row r="279" ht="12" customHeight="1" s="1"/>
   </sheetData>
